--- a/docs/最新版/02_管理シート/動線設計シート.xlsx
+++ b/docs/最新版/02_管理シート/動線設計シート.xlsx
@@ -551,14 +551,14 @@
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ぺいほーむ 動線設計シート</t>
+          <t>ぺいほーむ 動線設計シート (全員同一料金)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>目標収益 (件数) から逆算した動線設計とKPI管理。Phase 毎にどの動線をどこまで伸ばすかを定義</t>
+          <t>目標収益から逆算した動線設計とKPI管理</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>目標売上からフェーズ毎の必要件数を逆算</t>
+          <t>Phase別の月次売上目標と必要件数</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>ユーザーの入口から収益発生までの動線を可視化</t>
+          <t>ユーザーの入口から収益発生までの動線</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>見学会予約動線 / AI診断動線 / 動画動線 / 相談動線</t>
+          <t>MVP 17画面の動線</t>
         </is>
       </c>
     </row>
@@ -643,7 +643,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>P1の継続動線 + 記事動線 + 撮影プラン動線</t>
+          <t>P1 + 記事・ニュース・撮影プラン</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>P2の継続動線 + 物件動線 + 月額掲載動線</t>
+          <t>P2 + 物件・月額掲載・成果報酬</t>
         </is>
       </c>
     </row>
@@ -677,7 +677,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>P3の継続動線 + AI質問動線 + SaaS動線</t>
+          <t>P3 + AI質問・SaaS</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>全国展開期の動線</t>
+          <t>全国展開期</t>
         </is>
       </c>
     </row>
@@ -706,12 +706,12 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>ファネル逆算 (詳細)</t>
+          <t>ファネル逆算</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>UU→診断→予約→成約の各ステップ転換率</t>
+          <t>UU→診断→予約→成約 の各転換率</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>どの動線を優先してテコ入れするかのマトリクス</t>
+          <t>施策優先度マトリクス</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -767,7 +767,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>収益インパクト x 実装難易度 で動線施策を優先度付け</t>
+          <t>収益インパクト x 実装難易度</t>
         </is>
       </c>
     </row>
@@ -806,7 +806,7 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>YouTube動画の冒頭3秒でぺいほーむ紹介を毎本挿入</t>
+          <t>YouTube動画の冒頭でぺいほーむ紹介を毎本挿入</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>AI診断完了後の工務店カードに「見学会予約」ボタン併設</t>
+          <t>AI診断完了後の工務店カードに見学会予約ボタン併設</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
@@ -880,29 +880,29 @@
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>動画カードにサムネオーバーレイで「この家が気になる」CTA</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>YouTube動線</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>会員登録をAI診断完了時に強めに促す (Phase 3成果報酬対象)</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>AI診断→会員</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>低</t>
         </is>
       </c>
     </row>
@@ -914,12 +914,12 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>TOP の1st view に「見学会予約」CTA併設</t>
+          <t>動画カードにCTAオーバーレイで『この家が気になる』</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>見学会動線</t>
+          <t>YouTube動線</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -941,17 +941,17 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>AI診断の質問数を10→7問に減らす (離脱率改善)</t>
+          <t>TOP の1st view に見学会予約CTA併設</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>AI診断動線</t>
+          <t>見学会動線</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
@@ -968,76 +968,76 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>工務店詳細ページに「この工務店の見学会カレンダー」埋込</t>
+          <t>AI診断の質問数を10→7問に減らす (離脱率改善)</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
+          <t>AI診断動線</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>工務店詳細ページに見学会カレンダー埋込</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
           <t>工務店検索動線</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E12" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>無料相談のフォームを1画面でLINE連携</t>
-        </is>
-      </c>
-      <c r="C12" s="13" t="inlineStr">
-        <is>
-          <t>無料相談動線</t>
-        </is>
-      </c>
-      <c r="D12" s="13" t="inlineStr">
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>lead_source tracking 実装 (成果報酬の追跡基盤)</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>全動線</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>中</t>
-        </is>
-      </c>
-      <c r="E12" s="13" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>事例カードの下に「同じ工務店の動画を見る」リンク</t>
-        </is>
-      </c>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>事例動線</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
-        <is>
-          <t>低</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>Phase2: ニュース記事内のCTA実装 (工務店回遊)</t>
+          <t>無料相談フォームを1画面でLINE連携</t>
         </is>
       </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
-          <t>記事動線</t>
+          <t>無料相談動線</t>
         </is>
       </c>
       <c r="D14" s="13" t="inlineStr">
@@ -1076,76 +1076,76 @@
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>Phase2: 撮影プラン申込フォームの導線整備</t>
+          <t>事例カードに『同じ工務店の動画を見る』</t>
         </is>
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
+          <t>事例動線</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>Phase2: ニュース記事内のCTA実装</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>記事動線</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>Phase2: 撮影プラン申込フォーム導線整備</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
           <t>撮影動線</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="inlineStr">
-        <is>
-          <t>Phase3: 物件詳細の「近くの工務店」自動レコメンド</t>
-        </is>
-      </c>
-      <c r="C16" s="14" t="inlineStr">
-        <is>
-          <t>物件動線</t>
-        </is>
-      </c>
-      <c r="D16" s="14" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="E16" s="14" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B17" s="14" t="inlineStr">
-        <is>
-          <t>Phase3: 月額プランの体験版 (1ヶ月無料)</t>
-        </is>
-      </c>
-      <c r="C17" s="14" t="inlineStr">
-        <is>
-          <t>月額動線</t>
-        </is>
-      </c>
-      <c r="D17" s="14" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="E17" s="14" t="inlineStr">
-        <is>
-          <t>低</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>Phase4: AI質問のリアルタイム通知Push</t>
+          <t>Phase3: 物件詳細『近くの工務店』レコメンド</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>AI質問動線</t>
+          <t>物件動線</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
@@ -1184,74 +1184,155 @@
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
+          <t>Phase3: 月額プランの体験版 (1ヶ月無料)</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>月額動線</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E19" s="14" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>Phase3: 成約報告フォーム (工務店ダッシュボード)</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>成果報酬動線</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="E20" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>Phase4: AI質問のリアルタイム通知Push</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>AI質問動線</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E21" s="14" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
           <t>Phase4: SaaSデモ環境のセルフサインアップ</t>
         </is>
       </c>
-      <c r="C19" s="14" t="inlineStr">
+      <c r="C22" s="14" t="inlineStr">
         <is>
           <t>SaaS動線</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="D22" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
+      <c r="E22" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="15" t="inlineStr">
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B23" s="15" t="inlineStr">
         <is>
           <t>Phase5: 県別ランディングページ x 5県</t>
         </is>
       </c>
-      <c r="C20" s="15" t="inlineStr">
+      <c r="C23" s="15" t="inlineStr">
         <is>
           <t>県別SEO</t>
         </is>
       </c>
-      <c r="D20" s="15" t="inlineStr">
+      <c r="D23" s="15" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="E20" s="15" t="inlineStr">
+      <c r="E23" s="15" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B24" s="15" t="inlineStr">
         <is>
           <t>Phase5: Google広告のリマーケティング</t>
         </is>
       </c>
-      <c r="C21" s="15" t="inlineStr">
+      <c r="C24" s="15" t="inlineStr">
         <is>
           <t>有料広告</t>
         </is>
       </c>
-      <c r="D21" s="15" t="inlineStr">
+      <c r="D24" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="E21" s="15" t="inlineStr">
+      <c r="E24" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -1277,7 +1358,7 @@
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -1295,7 +1376,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Phase別の月次売上目標と、それを達成するために必要な件数</t>
+          <t>Phase別の月次売上目標と必要件数 (全員同一料金)</t>
         </is>
       </c>
     </row>
@@ -1317,27 +1398,27 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>見学会予約 件数</t>
+          <t>見学会予約</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>成果報酬 件数</t>
+          <t>成果報酬件数</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>撮影 本数</t>
+          <t>撮影本数</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>月額掲載 社数</t>
+          <t>月額掲載社数</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>SaaS 社数</t>
+          <t>SaaS社数</t>
         </is>
       </c>
     </row>
@@ -1354,11 +1435,11 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>¥0</t>
+          <t>¥500,000</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>0</v>
@@ -1374,34 +1455,34 @@
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>6月</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>¥175,000</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="6" t="n">
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>¥750,000</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E6" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="F6" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="G6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1418,14 +1499,14 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>¥325,000</t>
+          <t>¥1,150,000</t>
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>1</v>
@@ -1450,14 +1531,14 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>¥450,000</t>
+          <t>¥1,550,000</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>2</v>
@@ -1482,54 +1563,54 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>¥730,000</t>
+          <t>¥2,940,000</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>3</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>10月</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>¥840,000</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="E10" s="6" t="n">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>¥4,150,000</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="E10" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="F10" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G10" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="H10" s="6" t="n">
+      <c r="G10" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1546,20 +1627,20 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>¥1,180,000</t>
+          <t>¥4,640,000</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F11" s="7" t="n">
         <v>4</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H11" s="7" t="n">
         <v>0</v>
@@ -1578,23 +1659,23 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>¥1,490,000</t>
+          <t>¥5,950,000</t>
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F12" s="7" t="n">
         <v>4</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -1610,23 +1691,23 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>¥1,720,000</t>
+          <t>¥6,510,000</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F13" s="7" t="n">
         <v>5</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -1642,23 +1723,23 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>¥2,000,000</t>
+          <t>¥7,940,000</t>
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F14" s="7" t="n">
         <v>5</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -1674,23 +1755,23 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>¥2,360,000</t>
+          <t>¥8,500,000</t>
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F15" s="7" t="n">
         <v>6</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -1706,23 +1787,23 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>¥2,515,000</t>
+          <t>¥9,960,000</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F16" s="7" t="n">
         <v>6</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -1734,23 +1815,23 @@
       <c r="B17" s="8" t="inlineStr"/>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>¥13,785,000</t>
+          <t>¥54,540,000</t>
         </is>
       </c>
       <c r="D17" s="8" t="n">
-        <v>76</v>
+        <v>450</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="F17" s="8" t="n">
         <v>39</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1775,7 +1856,7 @@
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -1788,7 +1869,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ユーザーがどこから入って、どのページを経由して、どこで収益が発生するか</t>
+          <t>ユーザーがどこから入ってどこで収益が発生するか</t>
         </is>
       </c>
     </row>
@@ -1822,7 +1903,7 @@
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>YouTube (チャンネル)</t>
+          <t>YouTube チャンネル</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -1842,7 +1923,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>見学会予約費 + 成果報酬</t>
+          <t>見学会予約費 ¥50,000</t>
         </is>
       </c>
     </row>
@@ -1869,7 +1950,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>見学会予約費 + 成果報酬</t>
+          <t>¥50,000</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1977,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>見学会予約費 + 成果報酬</t>
+          <t>¥50,000</t>
         </is>
       </c>
     </row>
@@ -1918,19 +1999,19 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>診断結果 → 予約</t>
+          <t>診断結果 → 予約/問合せ</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>見学会予約費 + 成果報酬</t>
+          <t>¥50,000 + 成果報酬 3% (P3〜)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>AI家づくり診断 (広告)</t>
+          <t>AI家づくり診断</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -1945,66 +2026,66 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>お気に入り or 予約</t>
+          <t>お気に入り or 予約/相談</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>見学会予約費 + 成果報酬</t>
+          <t>¥50,000 + 成果報酬 3% (P3〜)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>LINE公式</t>
+          <t>無料相談</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>LINE内リンク</t>
+          <t>相談フォーム</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>ぺいほーむTOP → AI診断</t>
+          <t>スタッフ対応</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>相談予約</t>
+          <t>見学会予約 or 契約</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>送客先の工務店からの成果報酬</t>
+          <t>¥50,000 + 成果報酬 3% (P3〜)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>無料相談 (TOPCTA)</t>
+          <t>会員登録</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>相談フォーム</t>
+          <t>signup</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>スタッフ対応</t>
+          <t>マイページ活用 → 工務店連絡</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>見学会予約 or 契約</t>
+          <t>契約</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>見学会予約費 + 成果報酬</t>
+          <t>成果報酬 3% (P3〜)</t>
         </is>
       </c>
     </row>
@@ -2031,7 +2112,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>長期的送客</t>
+          <t>長期的送客 + 成果報酬 (P3〜)</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2139,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>撮影プラン販売機会</t>
+          <t>¥50,000</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2166,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>月額掲載料</t>
+          <t>月額掲載料 + 成果報酬 (会員成約)</t>
         </is>
       </c>
     </row>
@@ -2112,7 +2193,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>SaaSプラン</t>
+          <t>SaaSプラン + 成果報酬</t>
         </is>
       </c>
     </row>
@@ -2155,7 +2236,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>MVP 17画面の6動線。目標月間予約10件を各動線で分担</t>
+          <t>見学会予約 ¥50,000/件 のみ発生</t>
         </is>
       </c>
     </row>
@@ -2177,7 +2258,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>月間目標 (人数)</t>
+          <t>月間目標(UU)</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -2219,7 +2300,7 @@
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>動画視聴数 → ぺいほーむ遷移率</t>
+          <t>動画視聴数→遷移率</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
@@ -2239,12 +2320,12 @@
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
-          <t>3件</t>
+          <t>10件</t>
         </is>
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
-          <t>¥75,000〜¥125,000/月</t>
+          <t>¥500,000/月</t>
         </is>
       </c>
       <c r="I5" s="9" t="inlineStr">
@@ -2266,7 +2347,7 @@
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>診断完了数 → 工務店詳細遷移率</t>
+          <t>診断完了数</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -2286,12 +2367,12 @@
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>2件</t>
+          <t>3件</t>
         </is>
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>¥50,000〜¥100,000/月</t>
+          <t>¥150,000/月</t>
         </is>
       </c>
       <c r="I6" s="9" t="inlineStr">
@@ -2308,12 +2389,12 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>/builders 一覧</t>
+          <t>/builders</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>工務店詳細閲覧数</t>
+          <t>工務店詳細閲覧</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
@@ -2333,12 +2414,12 @@
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>1件</t>
+          <t>2件</t>
         </is>
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>¥25,000〜¥50,000/月</t>
+          <t>¥100,000/月</t>
         </is>
       </c>
       <c r="I7" s="9" t="inlineStr">
@@ -2355,12 +2436,12 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>/event 一覧</t>
+          <t>/event</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>見学会予約フォーム完了率</t>
+          <t>予約フォーム完了率</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
@@ -2385,7 +2466,7 @@
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>¥75,000〜¥125,000/月</t>
+          <t>¥150,000/月</t>
         </is>
       </c>
       <c r="I8" s="9" t="inlineStr">
@@ -2407,7 +2488,7 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>相談フォーム送信数</t>
+          <t>相談フォーム送信</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
@@ -2432,7 +2513,7 @@
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>¥25,000〜¥50,000/月</t>
+          <t>¥50,000/月 (P3〜は成果報酬対象)</t>
         </is>
       </c>
       <c r="I9" s="9" t="inlineStr">
@@ -2454,7 +2535,7 @@
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>事例閲覧 → 工務店遷移率</t>
+          <t>事例→工務店遷移率</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
@@ -2474,12 +2555,12 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>0件</t>
+          <t>1件</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>間接送客のみ</t>
+          <t>¥50,000/月</t>
         </is>
       </c>
       <c r="I10" s="9" t="inlineStr">
@@ -2527,7 +2608,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>記事・ニュース動線を追加。撮影プラン販売で客単価UP</t>
+          <t>撮影プラン開始</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2630,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>月間目標 (人数)</t>
+          <t>月間目標(UU)</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -2591,7 +2672,7 @@
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>動画視聴数 → ぺいほーむ遷移率</t>
+          <t>動画視聴数→遷移率</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
@@ -2611,12 +2692,12 @@
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
-          <t>3件</t>
+          <t>10件</t>
         </is>
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
-          <t>¥75,000〜¥125,000/月</t>
+          <t>¥500,000/月</t>
         </is>
       </c>
       <c r="I5" s="9" t="inlineStr">
@@ -2638,7 +2719,7 @@
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>診断完了数 → 工務店詳細遷移率</t>
+          <t>診断完了数</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -2658,12 +2739,12 @@
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>2件</t>
+          <t>3件</t>
         </is>
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>¥50,000〜¥100,000/月</t>
+          <t>¥150,000/月</t>
         </is>
       </c>
       <c r="I6" s="9" t="inlineStr">
@@ -2680,12 +2761,12 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>/builders 一覧</t>
+          <t>/builders</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>工務店詳細閲覧数</t>
+          <t>工務店詳細閲覧</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
@@ -2705,12 +2786,12 @@
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>1件</t>
+          <t>2件</t>
         </is>
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>¥25,000〜¥50,000/月</t>
+          <t>¥100,000/月</t>
         </is>
       </c>
       <c r="I7" s="9" t="inlineStr">
@@ -2727,12 +2808,12 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>/event 一覧</t>
+          <t>/event</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>見学会予約フォーム完了率</t>
+          <t>予約フォーム完了率</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
@@ -2757,7 +2838,7 @@
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>¥75,000〜¥125,000/月</t>
+          <t>¥150,000/月</t>
         </is>
       </c>
       <c r="I8" s="9" t="inlineStr">
@@ -2779,7 +2860,7 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>相談フォーム送信数</t>
+          <t>相談フォーム送信</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
@@ -2804,7 +2885,7 @@
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>¥25,000〜¥50,000/月</t>
+          <t>¥50,000/月 (P3〜は成果報酬対象)</t>
         </is>
       </c>
       <c r="I9" s="9" t="inlineStr">
@@ -2826,7 +2907,7 @@
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>事例閲覧 → 工務店遷移率</t>
+          <t>事例→工務店遷移率</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
@@ -2846,12 +2927,12 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>0件</t>
+          <t>1件</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>間接送客のみ</t>
+          <t>¥50,000/月</t>
         </is>
       </c>
       <c r="I10" s="9" t="inlineStr">
@@ -2868,12 +2949,12 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>/news 一覧</t>
+          <t>/news</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>ニュース閲覧 → 工務店遷移率</t>
+          <t>ニュース→工務店遷移</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
@@ -2898,7 +2979,7 @@
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>¥50,000〜¥100,000/月</t>
+          <t>¥100,000/月</t>
         </is>
       </c>
       <c r="I11" s="9" t="inlineStr">
@@ -2915,12 +2996,12 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>/articles 一覧</t>
+          <t>/articles</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>記事閲覧 → 工務店遷移率</t>
+          <t>記事→工務店遷移</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
@@ -2945,7 +3026,7 @@
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>¥75,000〜¥150,000/月</t>
+          <t>¥150,000/月</t>
         </is>
       </c>
       <c r="I12" s="9" t="inlineStr">
@@ -2962,17 +3043,17 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>工務店向けアウトバウンド</t>
+          <t>工務店アウトバウンド</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>撮影プラン申込数</t>
+          <t>撮影プラン申込</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>10社アプローチ</t>
+          <t>10社</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -2992,7 +3073,7 @@
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>¥150,000〜¥300,000/月</t>
+          <t>¥300,000/月</t>
         </is>
       </c>
       <c r="I13" s="9" t="inlineStr">
@@ -3016,7 +3097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3040,7 +3121,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>物件情報3動線を追加。月額掲載販売でストック収益開始</t>
+          <t>月額掲載 + 成果報酬 開始</t>
         </is>
       </c>
     </row>
@@ -3062,7 +3143,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>月間目標 (人数)</t>
+          <t>月間目標(UU)</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -3104,7 +3185,7 @@
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>動画視聴数 → ぺいほーむ遷移率</t>
+          <t>動画視聴数→遷移率</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
@@ -3124,12 +3205,12 @@
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
-          <t>3件</t>
+          <t>10件</t>
         </is>
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
-          <t>¥75,000〜¥125,000/月</t>
+          <t>¥500,000/月</t>
         </is>
       </c>
       <c r="I5" s="9" t="inlineStr">
@@ -3151,7 +3232,7 @@
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>診断完了数 → 工務店詳細遷移率</t>
+          <t>診断完了数</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -3171,12 +3252,12 @@
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>2件</t>
+          <t>3件</t>
         </is>
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>¥50,000〜¥100,000/月</t>
+          <t>¥150,000/月</t>
         </is>
       </c>
       <c r="I6" s="9" t="inlineStr">
@@ -3193,12 +3274,12 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>/builders 一覧</t>
+          <t>/builders</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>工務店詳細閲覧数</t>
+          <t>工務店詳細閲覧</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
@@ -3218,12 +3299,12 @@
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>1件</t>
+          <t>2件</t>
         </is>
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>¥25,000〜¥50,000/月</t>
+          <t>¥100,000/月</t>
         </is>
       </c>
       <c r="I7" s="9" t="inlineStr">
@@ -3240,12 +3321,12 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>/event 一覧</t>
+          <t>/event</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>見学会予約フォーム完了率</t>
+          <t>予約フォーム完了率</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
@@ -3270,7 +3351,7 @@
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>¥75,000〜¥125,000/月</t>
+          <t>¥150,000/月</t>
         </is>
       </c>
       <c r="I8" s="9" t="inlineStr">
@@ -3292,7 +3373,7 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>相談フォーム送信数</t>
+          <t>相談フォーム送信</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
@@ -3317,7 +3398,7 @@
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>¥25,000〜¥50,000/月</t>
+          <t>¥50,000/月 (P3〜は成果報酬対象)</t>
         </is>
       </c>
       <c r="I9" s="9" t="inlineStr">
@@ -3339,7 +3420,7 @@
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>事例閲覧 → 工務店遷移率</t>
+          <t>事例→工務店遷移率</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
@@ -3359,12 +3440,12 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>0件</t>
+          <t>1件</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>間接送客のみ</t>
+          <t>¥50,000/月</t>
         </is>
       </c>
       <c r="I10" s="9" t="inlineStr">
@@ -3381,12 +3462,12 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>/news 一覧</t>
+          <t>/news</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>ニュース閲覧 → 工務店遷移率</t>
+          <t>ニュース→工務店遷移</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
@@ -3411,7 +3492,7 @@
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>¥50,000〜¥100,000/月</t>
+          <t>¥100,000/月</t>
         </is>
       </c>
       <c r="I11" s="9" t="inlineStr">
@@ -3428,12 +3509,12 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>/articles 一覧</t>
+          <t>/articles</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>記事閲覧 → 工務店遷移率</t>
+          <t>記事→工務店遷移</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
@@ -3458,7 +3539,7 @@
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>¥75,000〜¥150,000/月</t>
+          <t>¥150,000/月</t>
         </is>
       </c>
       <c r="I12" s="9" t="inlineStr">
@@ -3475,17 +3556,17 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>工務店向けアウトバウンド</t>
+          <t>工務店アウトバウンド</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>撮影プラン申込数</t>
+          <t>撮影プラン申込</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>10社アプローチ</t>
+          <t>10社</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -3505,7 +3586,7 @@
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>¥150,000〜¥300,000/月</t>
+          <t>¥300,000/月</t>
         </is>
       </c>
       <c r="I13" s="9" t="inlineStr">
@@ -3522,12 +3603,12 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>/sale-homes 一覧</t>
+          <t>/sale-homes</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>物件詳細 → 問合せ率</t>
+          <t>物件→問合せ</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
@@ -3552,7 +3633,7 @@
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>¥100,000〜¥200,000/月</t>
+          <t>¥200,000/月</t>
         </is>
       </c>
       <c r="I14" s="9" t="inlineStr">
@@ -3569,12 +3650,12 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>/lands 一覧</t>
+          <t>/lands</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>土地詳細 → 問合せ率</t>
+          <t>土地→問合せ</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
@@ -3599,7 +3680,7 @@
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
-          <t>¥50,000〜¥100,000/月</t>
+          <t>¥100,000/月</t>
         </is>
       </c>
       <c r="I15" s="9" t="inlineStr">
@@ -3616,12 +3697,12 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>/features 一覧</t>
+          <t>/features</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>特集閲覧 → 工務店遷移率</t>
+          <t>特集→工務店</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
@@ -3646,7 +3727,7 @@
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>¥75,000〜¥150,000/月</t>
+          <t>¥150,000/月</t>
         </is>
       </c>
       <c r="I16" s="9" t="inlineStr">
@@ -3663,17 +3744,17 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>工務店向けアウトバウンド</t>
+          <t>工務店アウトバウンド</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>月額プラン加入社数</t>
+          <t>月額プラン加入</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>15社アプローチ</t>
+          <t>15社</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
@@ -3693,12 +3774,59 @@
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>¥150,000〜¥300,000/月</t>
+          <t>¥150,000/月</t>
         </is>
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
           <t>営業</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>成果報酬動線</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>無料相談/AI診断経由</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>成約数</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>60リード</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>1成約</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>¥900,000/件</t>
+        </is>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>PM+営業</t>
         </is>
       </c>
     </row>
@@ -3717,7 +3845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3741,7 +3869,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AI質問・ウェビナー動線を追加。SaaS販売で MRR 急成長期</t>
+          <t>SaaS開始、MRR成長期</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3891,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>月間目標 (人数)</t>
+          <t>月間目標(UU)</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -3805,7 +3933,7 @@
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>動画視聴数 → ぺいほーむ遷移率</t>
+          <t>動画視聴数→遷移率</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
@@ -3825,12 +3953,12 @@
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
-          <t>3件</t>
+          <t>10件</t>
         </is>
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
-          <t>¥75,000〜¥125,000/月</t>
+          <t>¥500,000/月</t>
         </is>
       </c>
       <c r="I5" s="9" t="inlineStr">
@@ -3852,7 +3980,7 @@
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>診断完了数 → 工務店詳細遷移率</t>
+          <t>診断完了数</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -3872,12 +4000,12 @@
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>2件</t>
+          <t>3件</t>
         </is>
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>¥50,000〜¥100,000/月</t>
+          <t>¥150,000/月</t>
         </is>
       </c>
       <c r="I6" s="9" t="inlineStr">
@@ -3894,12 +4022,12 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>/builders 一覧</t>
+          <t>/builders</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>工務店詳細閲覧数</t>
+          <t>工務店詳細閲覧</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
@@ -3919,12 +4047,12 @@
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>1件</t>
+          <t>2件</t>
         </is>
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>¥25,000〜¥50,000/月</t>
+          <t>¥100,000/月</t>
         </is>
       </c>
       <c r="I7" s="9" t="inlineStr">
@@ -3941,12 +4069,12 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>/event 一覧</t>
+          <t>/event</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>見学会予約フォーム完了率</t>
+          <t>予約フォーム完了率</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
@@ -3971,7 +4099,7 @@
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>¥75,000〜¥125,000/月</t>
+          <t>¥150,000/月</t>
         </is>
       </c>
       <c r="I8" s="9" t="inlineStr">
@@ -3993,7 +4121,7 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>相談フォーム送信数</t>
+          <t>相談フォーム送信</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
@@ -4018,7 +4146,7 @@
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>¥25,000〜¥50,000/月</t>
+          <t>¥50,000/月 (P3〜は成果報酬対象)</t>
         </is>
       </c>
       <c r="I9" s="9" t="inlineStr">
@@ -4040,7 +4168,7 @@
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>事例閲覧 → 工務店遷移率</t>
+          <t>事例→工務店遷移率</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
@@ -4060,12 +4188,12 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>0件</t>
+          <t>1件</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>間接送客のみ</t>
+          <t>¥50,000/月</t>
         </is>
       </c>
       <c r="I10" s="9" t="inlineStr">
@@ -4082,12 +4210,12 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>/news 一覧</t>
+          <t>/news</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>ニュース閲覧 → 工務店遷移率</t>
+          <t>ニュース→工務店遷移</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
@@ -4112,7 +4240,7 @@
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>¥50,000〜¥100,000/月</t>
+          <t>¥100,000/月</t>
         </is>
       </c>
       <c r="I11" s="9" t="inlineStr">
@@ -4129,12 +4257,12 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>/articles 一覧</t>
+          <t>/articles</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>記事閲覧 → 工務店遷移率</t>
+          <t>記事→工務店遷移</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
@@ -4159,7 +4287,7 @@
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>¥75,000〜¥150,000/月</t>
+          <t>¥150,000/月</t>
         </is>
       </c>
       <c r="I12" s="9" t="inlineStr">
@@ -4176,17 +4304,17 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>工務店向けアウトバウンド</t>
+          <t>工務店アウトバウンド</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>撮影プラン申込数</t>
+          <t>撮影プラン申込</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>10社アプローチ</t>
+          <t>10社</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -4206,7 +4334,7 @@
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>¥150,000〜¥300,000/月</t>
+          <t>¥300,000/月</t>
         </is>
       </c>
       <c r="I13" s="9" t="inlineStr">
@@ -4223,12 +4351,12 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>/sale-homes 一覧</t>
+          <t>/sale-homes</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>物件詳細 → 問合せ率</t>
+          <t>物件→問合せ</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
@@ -4253,7 +4381,7 @@
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>¥100,000〜¥200,000/月</t>
+          <t>¥200,000/月</t>
         </is>
       </c>
       <c r="I14" s="9" t="inlineStr">
@@ -4270,12 +4398,12 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>/lands 一覧</t>
+          <t>/lands</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>土地詳細 → 問合せ率</t>
+          <t>土地→問合せ</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
@@ -4300,7 +4428,7 @@
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
-          <t>¥50,000〜¥100,000/月</t>
+          <t>¥100,000/月</t>
         </is>
       </c>
       <c r="I15" s="9" t="inlineStr">
@@ -4317,12 +4445,12 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>/features 一覧</t>
+          <t>/features</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>特集閲覧 → 工務店遷移率</t>
+          <t>特集→工務店</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
@@ -4347,7 +4475,7 @@
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>¥75,000〜¥150,000/月</t>
+          <t>¥150,000/月</t>
         </is>
       </c>
       <c r="I16" s="9" t="inlineStr">
@@ -4364,17 +4492,17 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>工務店向けアウトバウンド</t>
+          <t>工務店アウトバウンド</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>月額プラン加入社数</t>
+          <t>月額プラン加入</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>15社アプローチ</t>
+          <t>15社</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
@@ -4394,7 +4522,7 @@
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>¥150,000〜¥300,000/月</t>
+          <t>¥150,000/月</t>
         </is>
       </c>
       <c r="I17" s="9" t="inlineStr">
@@ -4406,89 +4534,89 @@
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>AI質問動線</t>
+          <t>成果報酬動線</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>/mypage/questions</t>
+          <t>無料相談/AI診断経由</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>質問投稿数 → 回答率</t>
+          <t>成約数</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>200 質問</t>
+          <t>60リード</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>1成約</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>4件</t>
+          <t>−</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>¥100,000〜¥200,000/月</t>
+          <t>¥900,000/件</t>
         </is>
       </c>
       <c r="I18" s="9" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>PM+営業</t>
         </is>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>ウェビナー動線</t>
+          <t>AI質問動線</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>/webinar 一覧</t>
+          <t>/mypage/questions</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>参加申込数 → 成約率</t>
+          <t>質問投稿→回答率</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>500 UU</t>
+          <t>200 質問</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>160</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>3件</t>
+          <t>4件</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>¥75,000〜¥150,000/月</t>
+          <t>¥200,000/月</t>
         </is>
       </c>
       <c r="I19" s="9" t="inlineStr">
@@ -4500,45 +4628,92 @@
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
+          <t>ウェビナー動線</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>/webinar</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>参加申込→成約</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>500 UU</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>3件</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>¥150,000/月</t>
+        </is>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
           <t>SaaS動線</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>工務店向けアウトバウンド</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>SaaSプラン加入社数</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>20社アプローチ</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>工務店アウトバウンド</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>SaaS加入</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>20社</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="F20" s="9" t="inlineStr">
+      <c r="F21" s="9" t="inlineStr">
         <is>
           <t>5社</t>
         </is>
       </c>
-      <c r="G20" s="9" t="inlineStr">
+      <c r="G21" s="9" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="H20" s="9" t="inlineStr">
-        <is>
-          <t>¥250,000〜¥500,000/月</t>
-        </is>
-      </c>
-      <c r="I20" s="9" t="inlineStr">
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>¥500,000/月</t>
+        </is>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
         <is>
           <t>営業</t>
         </is>
@@ -4583,7 +4758,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>全国展開。県別SEO + 有料広告で総UUを4万→8万へ</t>
+          <t>全国展開</t>
         </is>
       </c>
     </row>
@@ -4605,7 +4780,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>月間目標 (人数)</t>
+          <t>月間目標(UU)</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -4647,7 +4822,7 @@
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>検索流入 → 工務店遷移率</t>
+          <t>検索流入→工務店</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
@@ -4672,7 +4847,7 @@
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
-          <t>¥375,000〜¥750,000/月</t>
+          <t>¥750,000/月</t>
         </is>
       </c>
       <c r="I5" s="9" t="inlineStr">
@@ -4684,17 +4859,17 @@
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>県別SEO動線 (熊本・宮崎・大分・佐賀)</t>
+          <t>県別SEO動線 (他県)</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>/area/[prefecture]</t>
+          <t>/area/*</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>検索流入 → 工務店遷移率</t>
+          <t>検索流入→工務店</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -4719,7 +4894,7 @@
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>¥500,000〜¥1,000,000/月</t>
+          <t>¥1,000,000/月</t>
         </is>
       </c>
       <c r="I6" s="9" t="inlineStr">
@@ -4731,12 +4906,12 @@
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>既存動線 (全動線合算)</t>
+          <t>既存動線 (合算)</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Phase1-4の全動線</t>
+          <t>P1〜P4</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -4766,7 +4941,7 @@
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>¥2,000,000〜¥3,000,000/月</t>
+          <t>¥3,000,000/月</t>
         </is>
       </c>
       <c r="I7" s="9" t="inlineStr">
@@ -4783,7 +4958,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Google Ads / Meta Ads</t>
+          <t>Google/Meta Ads</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
@@ -4813,7 +4988,7 @@
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>¥250,000〜¥500,000/月</t>
+          <t>¥500,000/月</t>
         </is>
       </c>
       <c r="I8" s="9" t="inlineStr">
@@ -4837,7 +5012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -4858,7 +5033,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UU → AI診断 → 工務店詳細 → 見学会予約 → 成約 の各ステップの転換率と必要数</t>
+          <t>UU→診断→会員登録→見学会予約→成約 の各転換率</t>
         </is>
       </c>
     </row>
@@ -4875,22 +5050,22 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>必要 成約件数</t>
+          <t>必要成約件数</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>必要 予約数</t>
+          <t>必要会員登録数</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>必要 AI診断数</t>
+          <t>必要AI診断数</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>必要 UU</t>
+          <t>必要UU</t>
         </is>
       </c>
     </row>
@@ -4907,12 +5082,12 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>3件</t>
+          <t>0件</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>10件</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -4934,17 +5109,17 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>20件</t>
+          <t>25件</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>6件</t>
+          <t>0件</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>20件</t>
+          <t>200</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -4971,12 +5146,12 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>12件</t>
+          <t>2件</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>40件</t>
+          <t>400</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -5003,12 +5178,12 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>17件</t>
+          <t>4件</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>55件</t>
+          <t>600</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -5035,12 +5210,12 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>21件</t>
+          <t>5件</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>70件</t>
+          <t>900</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -5132,17 +5307,34 @@
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>見学会予約 → 成約</t>
+          <t>UU → 会員登録</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>予約後の契約率 (工務店依存)</t>
+          <t>※ P3 から成果報酬の対象判定に重要</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>会員登録 → 成約</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>長期的</t>
         </is>
       </c>
     </row>
